--- a/data/trans_bre/IP09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 28,04</t>
+          <t>-42,28; 29,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-49,78; 16,52</t>
+          <t>-50,16; 17,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-77,73; 44,82</t>
+          <t>-77,57; 38,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,67; 70,94</t>
+          <t>-38,97; 70,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-89,55; 232,95</t>
+          <t>-100,0; 272,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,72; 39,18</t>
+          <t>-66,8; 48,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 402,51</t>
+          <t>-70,29; 536,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 12,12</t>
+          <t>-19,93; 11,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 16,31</t>
+          <t>-10,79; 14,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 18,84</t>
+          <t>-20,16; 17,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 25,87</t>
+          <t>-11,83; 24,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,46; 50,0</t>
+          <t>-54,28; 52,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 62,95</t>
+          <t>-28,17; 60,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 54,75</t>
+          <t>-40,59; 54,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 135,59</t>
+          <t>-32,36; 126,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 13,51</t>
+          <t>-26,9; 13,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 30,02</t>
+          <t>-19,76; 29,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-54,23; 16,73</t>
+          <t>-48,99; 17,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 27,5</t>
+          <t>-20,01; 30,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-86,7; 158,73</t>
+          <t>-85,23; 135,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 317,22</t>
+          <t>-63,72; 277,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 54,35</t>
+          <t>-70,55; 52,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 206,87</t>
+          <t>-54,52; 258,51</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 5,29</t>
+          <t>-16,19; 7,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 11,57</t>
+          <t>-9,3; 14,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 10,05</t>
+          <t>-20,76; 9,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 29,73</t>
+          <t>-6,82; 30,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 22,33</t>
+          <t>-49,43; 33,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 39,18</t>
+          <t>-24,83; 51,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,86; 26,04</t>
+          <t>-39,54; 27,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 133,41</t>
+          <t>-19,68; 143,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 29,29</t>
+          <t>-38,45; 29,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-50,16; 17,46</t>
+          <t>-51,03; 17,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-77,57; 38,97</t>
+          <t>-77,89; 41,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 70,53</t>
+          <t>-33,97; 69,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 272,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 48,27</t>
+          <t>-68,9; 42,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-70,29; 536,25</t>
+          <t>-62,54; 507,69</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 11,88</t>
+          <t>-20,4; 11,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 14,83</t>
+          <t>-12,37; 15,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 17,95</t>
+          <t>-18,52; 18,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 24,75</t>
+          <t>-12,15; 23,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,28; 52,52</t>
+          <t>-54,11; 52,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 60,55</t>
+          <t>-32,05; 59,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 54,81</t>
+          <t>-36,84; 53,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 126,49</t>
+          <t>-32,32; 129,21</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,9; 13,86</t>
+          <t>-29,38; 14,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 29,89</t>
+          <t>-16,36; 30,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 17,67</t>
+          <t>-46,94; 16,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 30,21</t>
+          <t>-19,34; 31,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-85,23; 135,97</t>
+          <t>-87,09; 154,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 277,35</t>
+          <t>-56,97; 328,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,55; 52,81</t>
+          <t>-71,22; 56,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,52; 258,51</t>
+          <t>-53,29; 262,45</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 7,57</t>
+          <t>-18,16; 6,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 14,19</t>
+          <t>-9,98; 12,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 9,82</t>
+          <t>-22,23; 10,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 30,64</t>
+          <t>-6,27; 28,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 33,17</t>
+          <t>-53,53; 28,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 51,69</t>
+          <t>-26,18; 46,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 27,42</t>
+          <t>-41,37; 26,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 143,75</t>
+          <t>-16,84; 127,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,08</t>
+          <t>-16,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>-30,09%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 29,84</t>
+          <t>-39,9; 28,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-51,03; 17,22</t>
+          <t>-49,78; 16,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 41,95</t>
+          <t>-77,73; 44,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,97; 69,54</t>
+          <t>-63,38; 33,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>-89,55; 232,95</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-67,72; 39,18</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-68,9; 42,84</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,54; 507,69</t>
+          <t>-100,0; 97,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 11,9</t>
+          <t>-20,78; 12,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 15,3</t>
+          <t>-12,51; 16,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 18,75</t>
+          <t>-20,59; 18,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 23,57</t>
+          <t>-11,52; 25,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 52,69</t>
+          <t>-56,46; 50,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 59,58</t>
+          <t>-31,32; 62,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 53,35</t>
+          <t>-40,26; 54,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 129,21</t>
+          <t>-31,03; 129,28</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 14,99</t>
+          <t>-29,26; 13,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 30,07</t>
+          <t>-17,68; 30,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 16,77</t>
+          <t>-54,23; 16,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 31,42</t>
+          <t>-22,93; 26,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-87,09; 154,07</t>
+          <t>-86,7; 158,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,97; 328,4</t>
+          <t>-61,15; 317,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 56,35</t>
+          <t>-73,29; 54,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 262,45</t>
+          <t>-60,88; 189,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 6,31</t>
+          <t>-18,11; 5,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 12,91</t>
+          <t>-12,28; 11,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 10,42</t>
+          <t>-20,83; 10,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 28,67</t>
+          <t>-12,18; 16,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 28,79</t>
+          <t>-54,18; 22,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 46,77</t>
+          <t>-30,34; 39,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 26,34</t>
+          <t>-39,86; 26,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 127,28</t>
+          <t>-31,07; 71,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-8,6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-18,12</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-21,86</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-16,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-25,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-30,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-40,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-30,09%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-8.601922651245236</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-18.12282503441865</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-21.85543649784957</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-16.12690488527216</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2599303686606759</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3013600894110652</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.4098823232831433</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.3009022431106136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-39,9; 28,04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-49,78; 16,52</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-77,73; 44,82</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-63,38; 33,27</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-89,55; 232,95</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-67,72; 39,18</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 97,5</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-39.9012400659477</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-49.78011972722229</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-77.73364178401354</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-63.37524445394385</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.8954643549128583</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.6772260185105127</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>28.04153012289714</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16.52248591042435</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>44.82266917498067</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>33.26528972804921</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.329492592468167</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3918317617327353</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>0.9750107487774567</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-3,83</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-12,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-20,78; 12,12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-12,51; 16,31</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-20,59; 18,84</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,52; 25,02</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-56,46; 50,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-31,32; 62,95</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-40,26; 54,75</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-31,03; 129,28</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.832852391667707</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.040583020472736</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.8116204075495403</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4.552133676574127</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1275354364745697</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.06277338889749222</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01866808771157664</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1574056701511151</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-7,05</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,18</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-16,55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-30,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-30,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-20.77831071041351</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-12.50726809975803</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-20.58938349553367</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.51754111184075</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5645529645952077</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3132083826772949</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4026291454248475</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3102733466313303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-29,26; 13,51</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-17,68; 30,02</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-54,23; 16,73</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-22,93; 26,87</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-86,7; 158,73</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-61,15; 317,22</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-73,29; 54,35</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-60,88; 189,73</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12.11540412376089</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>16.30530292037882</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>18.84249606700016</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>25.02073348072464</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4999608541643074</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.6295114608990836</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.547533401282516</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.292816996117937</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +815,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-6,04</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,73</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-20,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-12,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-7.051190235979988</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5.178204149840523</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-16.55306435671841</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.292102660711793</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3048266527508485</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2397311786901434</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.30289233288953</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1224926372310766</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-18,11; 5,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-12,28; 11,57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-20,83; 10,05</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-12,18; 16,65</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-54,18; 22,33</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-30,34; 39,18</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-39,86; 26,04</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-31,07; 71,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-29.26203624986434</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-17.6849551132687</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-54.23226149174226</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-22.9284892406463</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.867034513622553</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6115351867185885</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7328733706972705</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6088376434813816</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.50688475378608</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>30.01995171077615</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>16.73408323010863</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>26.86533632546335</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.587307745339261</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3.172232826144902</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5434745408726132</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.897349865142145</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-6.040741411813774</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8242902565791188</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-5.730119388064531</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.648246004663834</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2097490543700615</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.0246476801954528</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1239927707521249</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.05291615679989517</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-18.10511986856548</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-12.27504825643769</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-20.82886854121656</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-12.17984721302253</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5417869167199165</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3033766220092579</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3985723486115914</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3107259689036321</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.285040659027121</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>11.573702933456</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.0541918296175</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>16.65264557246027</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2232633405784972</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3918261493632707</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2603526425477261</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.7183602933250477</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1013,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
